--- a/output/docs/DOC_067_ASA_report.xlsx
+++ b/output/docs/DOC_067_ASA_report.xlsx
@@ -87,7 +87,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -95,6 +95,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -463,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -529,12 +532,12 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>FND-0014</t>
+          <t>FND-0015</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>CWE-200</t>
+          <t>CWE-693</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -544,12 +547,12 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>tcp/8443 admin console</t>
+          <t>http://127.0.0.1:8099 response headers</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>management console reachable from the application network</t>
+          <t>missing Content-Security-Policy header</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -558,6 +561,43 @@
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Remediate / upgrade; verified on retest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>FND-0016</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>CWE-319</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>http://127.0.0.1:8099 response headers</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>missing HSTS header</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Remediate / upgrade; verified on retest.</t>
         </is>
@@ -566,7 +606,44 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Total findings: 1</t>
+          <t>FND-0017</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>CWE-693</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>http://127.0.0.1:8099 response headers</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>missing X-Content-Type-Options header</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Remediate / upgrade; verified on retest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Total findings: 3</t>
         </is>
       </c>
     </row>
